--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,49 +1008,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84606583</v>
+        <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>110070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ravin nedan Högberget, Dlr</t>
+          <t>Knutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501478</v>
+        <v>501496</v>
       </c>
       <c r="R5" t="n">
-        <v>6723967</v>
+        <v>6724098</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1077,17 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-04-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-04-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i ravinsluttningarna</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,34 +1091,37 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84606583</t>
+          <t>https://artportalen.se/Sighting/136954261</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72497830</v>
+        <v>84606583</v>
       </c>
       <c r="B6" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,37 +1129,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder Rälta, Dlr</t>
+          <t>Ravin nedan Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501505</v>
+        <v>501478</v>
       </c>
       <c r="R6" t="n">
-        <v>6723949</v>
+        <v>6723967</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,17 +1187,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
+          <t>2020-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
+          <t>2020-04-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Paddbärsmalmätare.</t>
+          <t>Rikligt i ravinsluttningarna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,34 +1206,31 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trolldruvemätare (nationellt)</t>
-        </is>
-      </c>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72497830</t>
+          <t>https://artportalen.se/Sighting/84606583</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72497832</v>
+        <v>72497830</v>
       </c>
       <c r="B7" t="n">
         <v>101228</v>
@@ -1266,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501471</v>
+        <v>501505</v>
       </c>
       <c r="R7" t="n">
-        <v>6723968</v>
+        <v>6723949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,6 +1334,117 @@
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72497830</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>72497832</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6723968</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Paddbärsmalmätare.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare (nationellt)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/72497832</t>
         </is>
@@ -1348,6 +1458,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59840-2024 artfynd.xlsx
+++ b/artfynd/A 59840-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136954261</v>
       </c>
       <c r="B5" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
